--- a/artfynd/A 34292-2023 artfynd.xlsx
+++ b/artfynd/A 34292-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34292-2023 artfynd.xlsx
+++ b/artfynd/A 34292-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121150985</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2023 artfynd.xlsx
+++ b/artfynd/A 34292-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121150985</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2023 artfynd.xlsx
+++ b/artfynd/A 34292-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121150985</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2023 artfynd.xlsx
+++ b/artfynd/A 34292-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121150985</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2023 artfynd.xlsx
+++ b/artfynd/A 34292-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111658400</v>
+        <v>103464256</v>
       </c>
       <c r="B2" t="n">
-        <v>90295</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4740</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bornsviken, Vstm</t>
+          <t>Nedre Sundet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523326</v>
+        <v>523332</v>
       </c>
       <c r="R2" t="n">
-        <v>6619778</v>
+        <v>6619803</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,57 +776,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150985</v>
+        <v>111658400</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4740</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Morskoga, Vstm</t>
+          <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523296</v>
+        <v>523326</v>
       </c>
       <c r="R3" t="n">
-        <v>6619729</v>
+        <v>6619778</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,21 +858,981 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111350516</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>523320</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619811</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111350555</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>523346</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619799</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112299094</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>523332</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619814</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112279968</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>523344</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619785</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112280122</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>523356</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6619775</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112299188</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>523355</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619797</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119371589</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523305</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619720</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119371494</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>523309</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619735</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121150985</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Morskoga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>523296</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6619729</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34292-2023 artfynd.xlsx
+++ b/artfynd/A 34292-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103464256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111658400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350516</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350555</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299094</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279968</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280122</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299188</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371589</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371494</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,8 +1888,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>